--- a/inputs/table_mappings.xlsx
+++ b/inputs/table_mappings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,16 +474,6 @@
           <t>target_table</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>context_id</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>criticality</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,16 +519,6 @@
           <t>fact_sales</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>sample_fact_sales</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -584,16 +564,6 @@
           <t>dim_brand</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>sample_dim_brand_scd2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -637,16 +607,6 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>dim_market</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>sample_dim_market</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>medium</t>
         </is>
       </c>
     </row>
@@ -680,16 +640,6 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>new_bigquery_table</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>sample_bq_only_table</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>medium</t>
         </is>
       </c>
     </row>
